--- a/reports/excel/10472013940.xlsx
+++ b/reports/excel/10472013940.xlsx
@@ -76,9 +76,8 @@
     <t>Intelligent Report</t>
   </si>
   <si>
-    <t>Here is a two-paragraph summary of the bureau portfolio:
-The customer's tradeline portfolio consists of N=50 total tradelines (M live = 15, P closed = 35). The portfolio features a mix of loan products, including Commercial Vehicle Loan (44 accounts), Auto Loan (3 accounts), Credit Card (1 account), and Home Loan (2 accounts). Key highlights include a high sanctioned exposure amount of INR 39,89,74,518, with a total outstanding amount of INR 14,84,39,359. The customer has a significant unsecured obligation of INR 15,000, with an unsecured outstanding amount of 0%. Notably, the credit card utilization percentage is not available, and there are no DPD values above zero. The FOIR ratio is &gt;300%, indicating an over-leveraged business/guarantor profile.
-The customer's behavioral features raise some concerns. The % Missed Payments Last 18M is 6.55%, which flags as [CONCERN — some missed payments]. The % Trades with 0+ DPD in 24M (All) is 16.00, indicating a high risk of loan stacking ([HIGH RISK]). Additionally, the Trade-to-Enquiry Ratio (Unsec 24M) is 0.00%, which flags as [CONCERN — low conversion, possible rejections]. The Avg Interpurchase Time All Loans (24M) is 1.39 months, indicating a frequent acquisition of new loans ([CONCERN — frequent acquisitions]).</t>
+    <t>The customer's tradeline portfolio consists of N=50 total tradelines (M live=15, P closed=35). The portfolio features a mix of loan products, including Commercial Equipment Loan (43 accounts), Commercial Vehicle Loan (1 account), Home Loan (2 accounts), Auto Loan (3 accounts), and Credit Card (1 account). Key highlights include a high credit card utilization percentage, with 0% outstanding balance on the Credit Card product. Additionally, there are DPD values above zero for all loan products, indicating some level of delinquency. The customer has an obligation of INR 17,24,029 and a FOIR ratio of &gt;300%, indicating an over-leveraged business/guarantor profile.
+The behavioral insights suggest that the customer's credit behavior is characterized by [HIGH RISK] features, including high loan acquisition velocity (Avg Interpurchase Time All Loans: 1.39 months) and high % Trades with 0+ DPD in 12M (21.05%). The customer has also experienced some missed payments (6.55% of total trades), indicating a [CONCERN]. Furthermore, the trade-to-enquiry ratio is low (0.00%), suggesting possible rejections or concerns about creditworthiness ([CONCERN]). On the other hand, there are no notable [POSITIVE] features in this portfolio.</t>
   </si>
   <si>
     <t>91d DPD / Auto Loan / 17M ago</t>
@@ -87,13 +86,13 @@
     <t>&gt;300% — business/guarantor profile / Unsec: 0.0%</t>
   </si>
   <si>
-    <t>Sanctioned exposure peaked at ₹23.8Cr in Sep 2025, led by CMVL (₹22.4Cr) and AL (₹85.0L). Current exposure stands at ₹23.5Cr (CMVL, AL, HL active), down 1% from peak — trend stable.</t>
+    <t>Sanctioned exposure peaked at ₹23.8Cr in Sep 2025, led by CEL (₹22.0Cr) and AL (₹85.0L). Current exposure stands at ₹23.5Cr (CEL, CMVL, HL, AL active), down 1% from peak — trend stable.</t>
   </si>
   <si>
     <t>Housing Loan</t>
   </si>
   <si>
-    <t>Active delinquency detected with Max DPD of 91 days [Auto Loan: Opened: Apr 2023 – Oct 2023 | Active] | Auto Loan: Delinquent with Max DPD of 91 days [Opened: Apr 2023 – Oct 2023 | Active] | Commercial Vehicle Loan: Delinquent with Max DPD of 55 days [Opened: Aug 2012 – Sep 2025 | Last Closed: Dec 2025] | Home Loan: Delinquent with Max DPD of 51 days [Opened: Apr 2012 – Sep 2023 | Last Closed: Jan 2022]</t>
+    <t>Active delinquency detected with Max DPD of 91 days [Auto Loan: Opened: Apr 2023 – Oct 2023 | Active] | Auto Loan: Delinquent with Max DPD of 91 days [Opened: Apr 2023 – Oct 2023 | Active] | Commercial Equipment Loan: Delinquent with Max DPD of 55 days [Opened: Aug 2012 – Sep 2025 | Last Closed: Dec 2025] | Home Loan: Delinquent with Max DPD of 51 days [Opened: Apr 2012 – Sep 2023 | Last Closed: Jan 2022]</t>
   </si>
   <si>
     <t>reports/bureau_analyser_10472013940_report.html</t>
